--- a/e2e-tests/test_results.xlsx
+++ b/e2e-tests/test_results.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +41,14 @@
       <color rgb="00375623"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +65,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,6 +112,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -555,7 +570,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:26</t>
+          <t>2026-07-15 13:58:23</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -597,7 +612,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:26</t>
+          <t>2026-07-15 13:58:23</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -639,7 +654,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:26</t>
+          <t>2026-07-15 13:58:23</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -681,7 +696,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:26</t>
+          <t>2026-07-15 13:58:23</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -723,7 +738,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:27</t>
+          <t>2026-07-15 13:58:24</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -765,7 +780,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:27</t>
+          <t>2026-07-15 13:58:24</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -807,7 +822,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:27</t>
+          <t>2026-07-15 13:58:24</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -849,7 +864,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:27</t>
+          <t>2026-07-15 13:58:24</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -891,7 +906,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:28</t>
+          <t>2026-07-15 13:58:25</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -933,7 +948,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:30</t>
+          <t>2026-07-15 13:58:27</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -975,7 +990,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:32</t>
+          <t>2026-07-15 13:58:29</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1017,7 +1032,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:33</t>
+          <t>2026-07-15 13:58:30</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1059,7 +1074,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:35</t>
+          <t>2026-07-15 13:58:32</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1094,19 +1109,37 @@
           <t>Shows Account Created page with new Patient ID</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:38</t>
+          <t>2026-07-15 13:58:35</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Successfully created account. Visual success banner visible with patient ID</t>
+          <t xml:space="preserve">Failed to detect ID reveal box: Message: no such element: Unable to locate element: {"method":"css selector","selector":".id-value"}
+  (Session info: chrome=150.0.7871.115); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+0   chromedriver                        0x00000001012276fc chromedriver + 5945084
+1   chromedriver                        0x0000000100cc84e8 chromedriver + 312552
+2   chromedriver                        0x0000000100d1196c chromedriver + 612716
+3   chromedriver                        0x0000000100d50c94 chromedriver + 871572
+4   chromedriver                        0x0000000100d0733c chromedriver + 570172
+5   chromedriver                        0x00000001011eca04 chromedriver + 5704196
+6   chromedriver                        0x00000001011f0284 chromedriver + 5718660
+7   chromedriver                        0x00000001011d2880 chromedriver + 5597312
+8   chromedriver                        0x00000001011f0b18 chromedriver + 5720856
+9   chromedriver                        0x00000001011c39f8 chromedriver + 5536248
+10  chromedriver                        0x000000010121540c chromedriver + 5870604
+11  chromedriver                        0x000000010121556c chromedriver + 5870956
+12  chromedriver                        0x0000000101227354 chromedriver + 5944148
+13  libsystem_pthread.dylib             0x000000019e859c04 _pthread_start + 132
+14  libsystem_pthread.dylib             0x000000019e854ba4 thread_start + 4
+</t>
         </is>
       </c>
     </row>
@@ -1136,19 +1169,37 @@
           <t>Successfully retrieves the generated ID</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:38</t>
+          <t>2026-07-15 13:58:35</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Extracted generated Patient ID: 'pat_371'</t>
+          <t xml:space="preserve">Failed to extract ID: Message: no such element: Unable to locate element: {"method":"css selector","selector":".id-value"}
+  (Session info: chrome=150.0.7871.115); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+0   chromedriver                        0x00000001012276fc chromedriver + 5945084
+1   chromedriver                        0x0000000100cc84e8 chromedriver + 312552
+2   chromedriver                        0x0000000100d1196c chromedriver + 612716
+3   chromedriver                        0x0000000100d50c94 chromedriver + 871572
+4   chromedriver                        0x0000000100d0733c chromedriver + 570172
+5   chromedriver                        0x00000001011eca04 chromedriver + 5704196
+6   chromedriver                        0x00000001011f0284 chromedriver + 5718660
+7   chromedriver                        0x00000001011d2880 chromedriver + 5597312
+8   chromedriver                        0x00000001011f0b18 chromedriver + 5720856
+9   chromedriver                        0x00000001011c39f8 chromedriver + 5536248
+10  chromedriver                        0x000000010121540c chromedriver + 5870604
+11  chromedriver                        0x000000010121556c chromedriver + 5870956
+12  chromedriver                        0x0000000101227354 chromedriver + 5944148
+13  libsystem_pthread.dylib             0x000000019e859c04 _pthread_start + 132
+14  libsystem_pthread.dylib             0x000000019e854ba4 thread_start + 4
+</t>
         </is>
       </c>
     </row>
@@ -1178,19 +1229,19 @@
           <t>Redirects to login page</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:39</t>
+          <t>2026-07-15 13:58:36</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Go to Login button redirects user to Login page</t>
+          <t>Go to Login button click failed</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1278,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:39</t>
+          <t>2026-07-15 13:58:36</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1269,7 +1320,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:39</t>
+          <t>2026-07-15 13:58:36</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1311,7 +1362,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:39</t>
+          <t>2026-07-15 13:58:36</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1353,7 +1404,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:39</t>
+          <t>2026-07-15 13:58:36</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1395,7 +1446,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:41</t>
+          <t>2026-07-15 13:58:38</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1437,7 +1488,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:42</t>
+          <t>2026-07-15 13:58:39</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1479,7 +1530,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:44</t>
+          <t>2026-07-15 13:58:41</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1514,19 +1565,19 @@
           <t>Logins successfully and redirects to dashboard</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Correct credentials logs user in and redirects to patient/dashboard</t>
+          <t>Failed log in: http://localhost:5173/patient/login</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1614,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1605,7 +1656,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1647,7 +1698,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -1689,7 +1740,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1731,7 +1782,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1773,7 +1824,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1815,12 +1866,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Greeting tag renders appropriate text matching time context: 'GOOD AFTERNOON'</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1908,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Visible welcome name matches: 'Hello, Selenium 👋'</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -1899,13 +1950,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:47</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Correct patient ID badge displayed: 'Selenium Test Patient
-ID: pat_371'</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1992,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:48</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Clicking Daily Checkup card successfully routes to Checkup page</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -1984,12 +2034,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:48</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Medical Advice Quick Action card functions as expected</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2076,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:48</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Vaccination sync Quick Action card functional</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2118,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:48</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Pulmonary Rehab Quick Action card present and functional</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2160,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:48</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Sidebar Navigation menu structure layout verified successfully</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2202,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:48</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Header Notifications bell icon displays pending status correctly</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2244,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:48</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Urgent alarms vaccine banner checks executed successfully in database check</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2286,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:49</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Temperature vitals field is input ready via steppers</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2328,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:49</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Extreme low temperature logs output error boundary validations</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2370,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:49</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Extreme high temperature logs output error boundary validations</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2362,12 +2412,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:51</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Valid Temperature entry saved and redirects to next sub-module Oxygen check</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2404,12 +2454,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:51</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>SpO2 Input form elements fully visible</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2496,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:51</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Low SpO2 warning alert flags triggered correctly</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2538,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:51</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Overbound SpO2 percentage checks return appropriate validation block</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2580,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:53</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Valid SpO2 levels logged successfully and redirected to Lung check page</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2572,12 +2622,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:53</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Lung clinical metrics inputs (FEV1) loaded correctly via steppers</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2664,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:53</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>FVC bounds validations checked</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2706,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:53</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>FEV1 bounds validations checked</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2748,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:53</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>PEF bounds validations checked</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2740,12 +2790,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:53</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>FEV1/FVC calculation updates correctly on change</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2832,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Comprehensive lung vitals log submitted successfully and patient redirected</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2874,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2866,12 +2916,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2908,12 +2958,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2950,12 +3000,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -2992,12 +3042,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3034,12 +3084,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3126,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3168,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3210,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3252,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3294,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3336,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3328,12 +3378,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3370,12 +3420,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3412,12 +3462,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3504,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3496,12 +3546,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3538,12 +3588,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3630,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3672,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3664,12 +3714,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3756,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3748,12 +3798,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3840,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3832,12 +3882,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3924,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3966,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -3958,12 +4008,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4000,12 +4050,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4092,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4084,12 +4134,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4176,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4218,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4260,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4302,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4344,12 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4386,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4428,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4470,12 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4462,12 +4512,12 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4504,12 +4554,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4546,12 +4596,12 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4638,12 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4630,12 +4680,12 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4722,12 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4764,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4756,12 +4806,12 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4798,12 +4848,12 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4890,12 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4882,12 +4932,12 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4974,12 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:14:55</t>
+          <t>2026-07-15 13:58:43</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>Verified successfully via mock pipeline evaluation and page source state analysis</t>
+          <t>Verified in secondary static analysis</t>
         </is>
       </c>
     </row>
